--- a/analysis/results/cross_store_synchronization.xlsx
+++ b/analysis/results/cross_store_synchronization.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,38 +425,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>store_key</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alfatah</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>daraz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jalalsons</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>metro</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>naheed</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>alfatah</t>
         </is>
@@ -453,69 +470,103 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0025</v>
+        <v>0.4912</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9252</v>
+        <v>0.5972</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9519</v>
+        <v>0.9838</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7218</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>daraz</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0025</v>
+        <v>0.4912</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1358</v>
+        <v>0.6286</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6377</v>
+        <v>-0.076</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5818</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>metro</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>jalalsons</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9252</v>
+        <v>0.5972</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1358</v>
+        <v>0.6286</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5259</v>
+        <v>0.372</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7587</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>metro</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.076</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6478</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>naheed</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.9519</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.6377</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5259</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B6" t="n">
+        <v>0.7218</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5818</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7587</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6478</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
     </row>

--- a/analysis/results/cross_store_synchronization.xlsx
+++ b/analysis/results/cross_store_synchronization.xlsx
@@ -470,16 +470,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4912</v>
+        <v>0.1356</v>
       </c>
       <c r="D2" t="n">
         <v>0.5972</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9838</v>
+        <v>0.7398</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7218</v>
+        <v>0.7219</v>
       </c>
     </row>
     <row r="3">
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4912</v>
+        <v>0.1356</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6286</v>
+        <v>0.1371</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.076</v>
+        <v>-0.0481</v>
       </c>
       <c r="F3" t="n">
         <v>0.5818</v>
@@ -514,7 +514,7 @@
         <v>0.5972</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6286</v>
+        <v>0.1371</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9838</v>
+        <v>0.7398</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.076</v>
+        <v>-0.0481</v>
       </c>
       <c r="D5" t="n">
         <v>0.372</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7218</v>
+        <v>0.7219</v>
       </c>
       <c r="C6" t="n">
         <v>0.5818</v>
